--- a/tools/sim/out/trick-audit-r518.xlsx
+++ b/tools/sim/out/trick-audit-r518.xlsx
@@ -554,7 +554,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Any hand = the same 1,000 hands for every loadout. Planned = the best hand on each board for that loadout.</t>
+          <t>Random hand = the same 1,000 hands for every loadout. Chosen hand = the best hand on each board for that loadout.</t>
         </is>
       </c>
     </row>
@@ -586,12 +586,12 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Ratio vs rarity avg (any hand)</t>
+          <t>Ratio vs rarity avg (random hand)</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Ratio vs rarity avg (planned)</t>
+          <t>Ratio vs rarity avg (chosen hand)</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -611,27 +611,27 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>Score multiplier (any hand)</t>
+          <t>Score multiplier (random hand)</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>Score multiplier (planned)</t>
+          <t>Score multiplier (chosen hand)</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>Pays on % of hands (any)</t>
+          <t>Pays on % of hands (random)</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>Pays on % of hands (planned)</t>
+          <t>Pays on % of hands (chosen)</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>Multiplier when it pays (any)</t>
+          <t>Multiplier when it pays (random)</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1077,7 +1077,7 @@
       <c r="R12" s="3" t="inlineStr"/>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>x2 pips per Jack on the BOARD: x3.4 on a random board (1.8 Jacks), x16 with all four held, x2 more per extra Jack.</t>
+          <t>x2 pips per Jack on the BOARD: x3.4 on average (a Jack is on the board 90% of the time), x16 with all four held, x2 more per extra Jack.</t>
         </is>
       </c>
     </row>
@@ -8838,7 +8838,7 @@
       <c r="R125" s="3" t="inlineStr"/>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>+0.1 Focus per card scored, paid every hand, forever: the best Focus Trick.</t>
+          <t>+0.1 Focus per card scored, paid every hand, forever: the best Focus Trick (+30%).</t>
         </is>
       </c>
     </row>
@@ -11462,12 +11462,12 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Average multiplier (any hand)</t>
+          <t>Average multiplier (random hand)</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Average multiplier (planned)</t>
+          <t>Average multiplier (chosen hand)</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -11763,7 +11763,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Every pair of Tricks scored alone together on 200 shared hands. Extra multiplier = both together / (A alone x B alone).</t>
+          <t>Every pair of Tricks scored on the same 200 hands with just those two held. Extra multiplier = both together / (A alone x B alone).</t>
         </is>
       </c>
     </row>
@@ -18447,7 +18447,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Points mean is pulled up by a few huge hands; the Tricks sheet shows the median over the Trick's 30 loadouts.</t>
+          <t>Points mean is pulled up by a few huge hands; the Tricks sheet shows the median over the Trick's 30 or more loadouts.</t>
         </is>
       </c>
     </row>
@@ -18474,12 +18474,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Points mean (any)</t>
+          <t>Points mean (random)</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Points median of loadouts (any)</t>
+          <t>Points median of loadouts (random)</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -18494,7 +18494,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>Multiplier (any)</t>
+          <t>Multiplier (random)</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -18524,22 +18524,22 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>Biggest single-hand share (any)</t>
+          <t>Biggest single-hand share (random)</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>Points mean (planned)</t>
+          <t>Points mean (chosen)</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>Multiplier (planned)</t>
+          <t>Multiplier (chosen)</t>
         </is>
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>Biggest single-hand share (planned)</t>
+          <t>Biggest single-hand share (chosen)</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
